--- a/allotted_holdings.xlsx
+++ b/allotted_holdings.xlsx
@@ -8,12 +8,12 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\bruce\PycharmProjects\CapitalFund\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{00CEC4AF-A6AE-4F7C-AC1F-FCF226596FED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{63031058-D17C-450C-B712-81ACABB5ED55}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{F686B110-DBA0-4814-A4B4-CBDB872F742B}"/>
   </bookViews>
   <sheets>
-    <sheet name="01" sheetId="1" r:id="rId1"/>
+    <sheet name="1" sheetId="1" r:id="rId1"/>
     <sheet name="Sheet1" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7" uniqueCount="7">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11" uniqueCount="11">
   <si>
     <t>security_name</t>
   </si>
@@ -47,6 +47,18 @@
   </si>
   <si>
     <t>uc_lc_monitoring</t>
+  </si>
+  <si>
+    <t>lot_size</t>
+  </si>
+  <si>
+    <t>issue_price</t>
+  </si>
+  <si>
+    <t>shares_allocated</t>
+  </si>
+  <si>
+    <t>lot_issued</t>
   </si>
 </sst>
 </file>
@@ -411,40 +423,47 @@
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1"/>
-      <c r="C1" s="1"/>
+      <c r="B1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>8</v>
+      </c>
       <c r="D1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="G1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="I1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="J1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="K1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="L1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="J1" s="1"/>
-      <c r="K1" s="1"/>
-      <c r="L1" s="1"/>
       <c r="M1" s="1"/>
       <c r="N1" s="1"/>
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="D2">
-        <v>0</v>
-      </c>
-      <c r="E2">
-        <v>0</v>
-      </c>
-      <c r="F2">
+      <c r="G2">
+        <v>1</v>
+      </c>
+      <c r="H2">
+        <v>1</v>
+      </c>
+      <c r="I2">
         <v>0</v>
       </c>
     </row>

--- a/allotted_holdings.xlsx
+++ b/allotted_holdings.xlsx
@@ -8,13 +8,13 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\bruce\PycharmProjects\CapitalFund\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{63031058-D17C-450C-B712-81ACABB5ED55}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3CD7C598-700A-4D43-A163-1292F71A09A1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{F686B110-DBA0-4814-A4B4-CBDB872F742B}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{F686B110-DBA0-4814-A4B4-CBDB872F742B}"/>
   </bookViews>
   <sheets>
     <sheet name="1" sheetId="1" r:id="rId1"/>
-    <sheet name="Sheet1" sheetId="2" r:id="rId2"/>
+    <sheet name="2" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -26,14 +26,11 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11" uniqueCount="11">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="9">
   <si>
     <t>security_name</t>
   </si>
   <si>
-    <t>allotted</t>
-  </si>
-  <si>
     <t>special_session_status</t>
   </si>
   <si>
@@ -46,9 +43,6 @@
     <t>regular_session_status</t>
   </si>
   <si>
-    <t>uc_lc_monitoring</t>
-  </si>
-  <si>
     <t>lot_size</t>
   </si>
   <si>
@@ -58,7 +52,7 @@
     <t>shares_allocated</t>
   </si>
   <si>
-    <t>lot_issued</t>
+    <t>lots_issued</t>
   </si>
 </sst>
 </file>
@@ -413,7 +407,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BD8C0391-31F7-4CC2-B7A6-D377C5AE8EA1}">
-  <dimension ref="A1:N2"/>
+  <dimension ref="A1:N1"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="13.88671875" customWidth="1"/>
@@ -424,16 +418,16 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D1" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>8</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>10</v>
       </c>
       <c r="G1" s="1" t="s">
         <v>1</v>
@@ -447,25 +441,9 @@
       <c r="J1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="K1" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="L1" s="1" t="s">
-        <v>6</v>
-      </c>
+      <c r="L1" s="1"/>
       <c r="M1" s="1"/>
       <c r="N1" s="1"/>
-    </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="G2">
-        <v>1</v>
-      </c>
-      <c r="H2">
-        <v>1</v>
-      </c>
-      <c r="I2">
-        <v>0</v>
-      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -474,9 +452,39 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FFD0B28E-1EE6-4A17-8779-D1B15393325C}">
-  <dimension ref="A1"/>
+  <dimension ref="A1:J1"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <sheetData/>
+  <sheetData>
+    <row r="1" spans="1:10" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/allotted_holdings.xlsx
+++ b/allotted_holdings.xlsx
@@ -1,22 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
-  <workbookPr defaultThemeVersion="166925"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\bruce\PycharmProjects\CapitalFund\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Pr\Work\pr\CapitalFund1\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3CD7C598-700A-4D43-A163-1292F71A09A1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{F686B110-DBA0-4814-A4B4-CBDB872F742B}"/>
+    <workbookView xWindow="-105" yWindow="-105" windowWidth="23250" windowHeight="12450"/>
   </bookViews>
   <sheets>
     <sheet name="1" sheetId="1" r:id="rId1"/>
     <sheet name="2" sheetId="2" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="162913"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -58,7 +57,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <fonts count="1" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -406,14 +405,21 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BD8C0391-31F7-4CC2-B7A6-D377C5AE8EA1}">
-  <dimension ref="A1:N1"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:N24"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="13.88671875" customWidth="1"/>
+    <col min="1" max="1" width="13.85546875" customWidth="1"/>
+    <col min="3" max="3" width="13.85546875" customWidth="1"/>
+    <col min="4" max="4" width="16.5703125" customWidth="1"/>
+    <col min="5" max="5" width="15.28515625" customWidth="1"/>
+    <col min="7" max="7" width="23.5703125" customWidth="1"/>
+    <col min="8" max="8" width="26.28515625" customWidth="1"/>
+    <col min="9" max="9" width="21.85546875" customWidth="1"/>
+    <col min="10" max="10" width="22.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:14" ht="60" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -444,6 +450,121 @@
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
       <c r="N1" s="1"/>
+    </row>
+    <row r="2" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="G2">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="G3">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="G4">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="G5">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="G6">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="7" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="G7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="G8">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="G9">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="G10">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="11" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="G11">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="12" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="G12">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="13" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="G13">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="14" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="G14">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="15" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="G15">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="16" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="G16">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="17" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G17">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="18" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G18">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="19" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G19">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="20" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G20">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="21" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G21">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="22" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G22">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="23" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G23">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="24" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G24">
+        <v>5</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -451,11 +572,11 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FFD0B28E-1EE6-4A17-8779-D1B15393325C}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:J1"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:10" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:10" ht="60" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>

--- a/allotted_holdings.xlsx
+++ b/allotted_holdings.xlsx
@@ -1,19 +1,19 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
-  <workbookPr/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29127"/>
+  <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Pr\Work\pr\CapitalFund1\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\bruce\PycharmProjects\CapitalFund\"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{49718896-1613-43DF-991E-00F7C87E0381}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-105" yWindow="-105" windowWidth="23250" windowHeight="12450"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="1" sheetId="1" r:id="rId1"/>
-    <sheet name="2" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="9">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11" uniqueCount="11">
   <si>
     <t>security_name</t>
   </si>
@@ -52,12 +52,18 @@
   </si>
   <si>
     <t>lots_issued</t>
+  </si>
+  <si>
+    <t>TATATECH</t>
+  </si>
+  <si>
+    <t>exchange</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="1" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -405,21 +411,21 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:N24"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="13.85546875" customWidth="1"/>
-    <col min="3" max="3" width="13.85546875" customWidth="1"/>
-    <col min="4" max="4" width="16.5703125" customWidth="1"/>
-    <col min="5" max="5" width="15.28515625" customWidth="1"/>
-    <col min="7" max="7" width="23.5703125" customWidth="1"/>
-    <col min="8" max="8" width="26.28515625" customWidth="1"/>
-    <col min="9" max="9" width="21.85546875" customWidth="1"/>
-    <col min="10" max="10" width="22.140625" customWidth="1"/>
+    <col min="1" max="1" width="13.88671875" customWidth="1"/>
+    <col min="3" max="3" width="13.88671875" customWidth="1"/>
+    <col min="4" max="4" width="16.5546875" customWidth="1"/>
+    <col min="5" max="5" width="15.33203125" customWidth="1"/>
+    <col min="7" max="7" width="23.5546875" customWidth="1"/>
+    <col min="8" max="8" width="26.33203125" customWidth="1"/>
+    <col min="9" max="9" width="21.88671875" customWidth="1"/>
+    <col min="10" max="10" width="22.109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" ht="60" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -434,6 +440,9 @@
       </c>
       <c r="E1" s="1" t="s">
         <v>8</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>10</v>
       </c>
       <c r="G1" s="1" t="s">
         <v>1</v>
@@ -451,158 +460,134 @@
       <c r="M1" s="1"/>
       <c r="N1" s="1"/>
     </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2">
+        <v>200</v>
+      </c>
+      <c r="C2">
+        <v>400</v>
+      </c>
+      <c r="D2">
+        <v>500</v>
+      </c>
+      <c r="E2">
+        <v>2</v>
+      </c>
       <c r="G2">
         <v>5</v>
       </c>
     </row>
-    <row r="3" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:14" x14ac:dyDescent="0.3">
       <c r="G3">
         <v>5</v>
       </c>
     </row>
-    <row r="4" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:14" x14ac:dyDescent="0.3">
       <c r="G4">
         <v>5</v>
       </c>
     </row>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:14" x14ac:dyDescent="0.3">
       <c r="G5">
         <v>5</v>
       </c>
     </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:14" x14ac:dyDescent="0.3">
       <c r="G6">
         <v>5</v>
       </c>
     </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:14" x14ac:dyDescent="0.3">
       <c r="G7">
         <v>5</v>
       </c>
     </row>
-    <row r="8" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:14" x14ac:dyDescent="0.3">
       <c r="G8">
         <v>5</v>
       </c>
     </row>
-    <row r="9" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:14" x14ac:dyDescent="0.3">
       <c r="G9">
         <v>5</v>
       </c>
     </row>
-    <row r="10" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:14" x14ac:dyDescent="0.3">
       <c r="G10">
         <v>5</v>
       </c>
     </row>
-    <row r="11" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:14" x14ac:dyDescent="0.3">
       <c r="G11">
         <v>5</v>
       </c>
     </row>
-    <row r="12" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:14" x14ac:dyDescent="0.3">
       <c r="G12">
         <v>5</v>
       </c>
     </row>
-    <row r="13" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:14" x14ac:dyDescent="0.3">
       <c r="G13">
         <v>5</v>
       </c>
     </row>
-    <row r="14" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:14" x14ac:dyDescent="0.3">
       <c r="G14">
         <v>5</v>
       </c>
     </row>
-    <row r="15" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:14" x14ac:dyDescent="0.3">
       <c r="G15">
         <v>5</v>
       </c>
     </row>
-    <row r="16" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:14" x14ac:dyDescent="0.3">
       <c r="G16">
         <v>5</v>
       </c>
     </row>
-    <row r="17" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="17" spans="7:7" x14ac:dyDescent="0.3">
       <c r="G17">
         <v>5</v>
       </c>
     </row>
-    <row r="18" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="18" spans="7:7" x14ac:dyDescent="0.3">
       <c r="G18">
         <v>5</v>
       </c>
     </row>
-    <row r="19" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="19" spans="7:7" x14ac:dyDescent="0.3">
       <c r="G19">
         <v>5</v>
       </c>
     </row>
-    <row r="20" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="20" spans="7:7" x14ac:dyDescent="0.3">
       <c r="G20">
         <v>5</v>
       </c>
     </row>
-    <row r="21" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="21" spans="7:7" x14ac:dyDescent="0.3">
       <c r="G21">
         <v>5</v>
       </c>
     </row>
-    <row r="22" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="22" spans="7:7" x14ac:dyDescent="0.3">
       <c r="G22">
         <v>5</v>
       </c>
     </row>
-    <row r="23" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="23" spans="7:7" x14ac:dyDescent="0.3">
       <c r="G23">
         <v>5</v>
       </c>
     </row>
-    <row r="24" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="24" spans="7:7" x14ac:dyDescent="0.3">
       <c r="G24">
         <v>5</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:J1"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <sheetData>
-    <row r="1" spans="1:10" ht="60" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>4</v>
       </c>
     </row>
   </sheetData>

--- a/allotted_holdings.xlsx
+++ b/allotted_holdings.xlsx
@@ -1,81 +1,33 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29127"/>
-  <workbookPr defaultThemeVersion="166925"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\bruce\PycharmProjects\CapitalFund\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{49718896-1613-43DF-991E-00F7C87E0381}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <workbookPr/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="1" sheetId="1" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="162913"/>
-  <extLst>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
-      <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
-  </extLst>
+  <definedNames/>
+  <calcPr calcId="162913" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11" uniqueCount="11">
-  <si>
-    <t>security_name</t>
-  </si>
-  <si>
-    <t>special_session_status</t>
-  </si>
-  <si>
-    <t>regular_session_monitoring</t>
-  </si>
-  <si>
-    <t>regular_session_day</t>
-  </si>
-  <si>
-    <t>regular_session_status</t>
-  </si>
-  <si>
-    <t>lot_size</t>
-  </si>
-  <si>
-    <t>issue_price</t>
-  </si>
-  <si>
-    <t>shares_allocated</t>
-  </si>
-  <si>
-    <t>lots_issued</t>
-  </si>
-  <si>
-    <t>TATATECH</t>
-  </si>
-  <si>
-    <t>exchange</t>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="0"/>
+  <fonts count="1">
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <color theme="1"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -94,24 +46,83 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="2">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -411,182 +422,226 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:N24"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:AI24"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="13.88671875" customWidth="1"/>
-    <col min="3" max="3" width="13.88671875" customWidth="1"/>
-    <col min="4" max="4" width="16.5546875" customWidth="1"/>
-    <col min="5" max="5" width="15.33203125" customWidth="1"/>
-    <col min="7" max="7" width="23.5546875" customWidth="1"/>
-    <col min="8" max="8" width="26.33203125" customWidth="1"/>
-    <col min="9" max="9" width="21.88671875" customWidth="1"/>
-    <col min="10" max="10" width="22.109375" customWidth="1"/>
+    <col width="13.88671875" customWidth="1" min="1" max="1"/>
+    <col width="13.88671875" customWidth="1" min="3" max="3"/>
+    <col width="16.5546875" customWidth="1" min="4" max="4"/>
+    <col width="15.33203125" customWidth="1" min="5" max="5"/>
+    <col width="23.5546875" customWidth="1" min="7" max="7"/>
+    <col width="26.33203125" customWidth="1" min="8" max="8"/>
+    <col width="21.88671875" customWidth="1" min="9" max="9"/>
+    <col width="22.109375" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A1" s="1" t="s">
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>security_name</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>lot_size</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>issue_price</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>shares_allocated</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>lots_issued</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>exchange</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>special_session_status</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>regular_session_monitoring</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>regular_session_day</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>regular_session_status</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="n"/>
+      <c r="M1" s="1" t="n"/>
+      <c r="N1" s="1" t="n"/>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>TATATECH</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>200</v>
+      </c>
+      <c r="C2" t="n">
+        <v>400</v>
+      </c>
+      <c r="D2" t="n">
+        <v>500</v>
+      </c>
+      <c r="E2" t="n">
+        <v>2</v>
+      </c>
+      <c r="G2" t="n">
+        <v>5</v>
+      </c>
+      <c r="W2" t="n">
+        <v>1</v>
+      </c>
+      <c r="X2" t="n">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="L1" s="1"/>
-      <c r="M1" s="1"/>
-      <c r="N1" s="1"/>
-    </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
-        <v>9</v>
-      </c>
-      <c r="B2">
-        <v>200</v>
-      </c>
-      <c r="C2">
-        <v>400</v>
-      </c>
-      <c r="D2">
-        <v>500</v>
-      </c>
-      <c r="E2">
-        <v>2</v>
-      </c>
-      <c r="G2">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="3" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="G3">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="4" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="G4">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="G5">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="G6">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="G7">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="8" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="G8">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="9" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="G9">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="10" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="G10">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="11" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="G11">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="12" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="G12">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="13" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="G13">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="14" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="G14">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="15" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="G15">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="16" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="G16">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="17" spans="7:7" x14ac:dyDescent="0.3">
-      <c r="G17">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="18" spans="7:7" x14ac:dyDescent="0.3">
-      <c r="G18">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="19" spans="7:7" x14ac:dyDescent="0.3">
-      <c r="G19">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="20" spans="7:7" x14ac:dyDescent="0.3">
-      <c r="G20">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="21" spans="7:7" x14ac:dyDescent="0.3">
-      <c r="G21">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="22" spans="7:7" x14ac:dyDescent="0.3">
-      <c r="G22">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="23" spans="7:7" x14ac:dyDescent="0.3">
-      <c r="G23">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="24" spans="7:7" x14ac:dyDescent="0.3">
-      <c r="G24">
+      <c r="Y2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI2" t="n">
+        <v>12.1575</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="G3" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="G4" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="G5" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="G6" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="G7" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="G8" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="G9" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="G10" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="G11" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="G12" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="G13" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="G14" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="G15" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="G16" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="G17" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="G18" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="G19" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="G20" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="G21" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="G22" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="G23" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="G24" t="n">
         <v>5</v>
       </c>
     </row>

--- a/allotted_holdings.xlsx
+++ b/allotted_holdings.xlsx
@@ -1,36 +1,106 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <workbookPr/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
+  <workbookPr defaultThemeVersion="166925"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\CapitalFund1\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B5BB23AA-8CD6-44A9-87D6-96040B8AF06E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView xWindow="-38520" yWindow="2340" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <definedNames/>
-  <calcPr calcId="162913" fullCalcOnLoad="1"/>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="12">
+  <si>
+    <t>security_name</t>
+  </si>
+  <si>
+    <t>lot_size</t>
+  </si>
+  <si>
+    <t>issue_price</t>
+  </si>
+  <si>
+    <t>shares_allocated</t>
+  </si>
+  <si>
+    <t>lots_issued</t>
+  </si>
+  <si>
+    <t>exchange</t>
+  </si>
+  <si>
+    <t>special_session_status</t>
+  </si>
+  <si>
+    <t>regular_session_monitoring</t>
+  </si>
+  <si>
+    <t>regular_session_day</t>
+  </si>
+  <si>
+    <t>regular_session_status</t>
+  </si>
+  <si>
+    <t>TATATECH</t>
+  </si>
+  <si>
+    <t>stock_category</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
-  <fonts count="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="1" x14ac:knownFonts="1">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <color theme="1"/>
-      <sz val="11"/>
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="6">
     <fill>
-      <patternFill/>
+      <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF92D050"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -45,84 +115,37 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+  <cellXfs count="6">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
-  <colors>
-    <indexedColors>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008000"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00808000"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="00C0C0C0"/>
-      <rgbColor rgb="00808080"/>
-      <rgbColor rgb="009999FF"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00FFFFCC"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00660066"/>
-      <rgbColor rgb="00FF8080"/>
-      <rgbColor rgb="000066CC"/>
-      <rgbColor rgb="00CCCCFF"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="0000CCFF"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00CCFFCC"/>
-      <rgbColor rgb="00FFFF99"/>
-      <rgbColor rgb="0099CCFF"/>
-      <rgbColor rgb="00FF99CC"/>
-      <rgbColor rgb="00CC99FF"/>
-      <rgbColor rgb="00FFCC99"/>
-      <rgbColor rgb="003366FF"/>
-      <rgbColor rgb="0033CCCC"/>
-      <rgbColor rgb="0099CC00"/>
-      <rgbColor rgb="00FFCC00"/>
-      <rgbColor rgb="00FF9900"/>
-      <rgbColor rgb="00FF6600"/>
-      <rgbColor rgb="00666699"/>
-      <rgbColor rgb="00969696"/>
-      <rgbColor rgb="00003366"/>
-      <rgbColor rgb="00339966"/>
-      <rgbColor rgb="00003300"/>
-      <rgbColor rgb="00333300"/>
-      <rgbColor rgb="00993300"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00333399"/>
-      <rgbColor rgb="00333333"/>
-    </indexedColors>
-  </colors>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -422,226 +445,204 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:AI24"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:AJ24"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col width="13.88671875" customWidth="1" min="1" max="1"/>
-    <col width="13.88671875" customWidth="1" min="3" max="3"/>
-    <col width="16.5546875" customWidth="1" min="4" max="4"/>
-    <col width="15.33203125" customWidth="1" min="5" max="5"/>
-    <col width="23.5546875" customWidth="1" min="7" max="7"/>
-    <col width="26.33203125" customWidth="1" min="8" max="8"/>
-    <col width="21.88671875" customWidth="1" min="9" max="9"/>
-    <col width="22.109375" customWidth="1" min="10" max="10"/>
+    <col min="1" max="1" width="13.88671875" customWidth="1"/>
+    <col min="3" max="3" width="13.88671875" customWidth="1"/>
+    <col min="4" max="4" width="16.5546875" customWidth="1"/>
+    <col min="5" max="5" width="15.33203125" customWidth="1"/>
+    <col min="7" max="7" width="13.44140625" customWidth="1"/>
+    <col min="8" max="8" width="23.5546875" customWidth="1"/>
+    <col min="9" max="9" width="26.33203125" customWidth="1"/>
+    <col min="10" max="10" width="21.88671875" customWidth="1"/>
+    <col min="11" max="11" width="22.109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>security_name</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>lot_size</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>issue_price</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>shares_allocated</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>lots_issued</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>exchange</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>special_session_status</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>regular_session_monitoring</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>regular_session_day</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>regular_session_status</t>
-        </is>
-      </c>
-      <c r="L1" s="1" t="n"/>
-      <c r="M1" s="1" t="n"/>
-      <c r="N1" s="1" t="n"/>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>TATATECH</t>
-        </is>
-      </c>
-      <c r="B2" t="n">
+    <row r="1" spans="1:36" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A1" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H1" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="I1" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="J1" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="K1" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="M1" s="1"/>
+      <c r="N1" s="1"/>
+      <c r="O1" s="1"/>
+    </row>
+    <row r="2" spans="1:36" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>10</v>
+      </c>
+      <c r="B2">
         <v>200</v>
       </c>
-      <c r="C2" t="n">
+      <c r="C2">
         <v>400</v>
       </c>
-      <c r="D2" t="n">
+      <c r="D2">
         <v>500</v>
       </c>
-      <c r="E2" t="n">
+      <c r="E2">
         <v>2</v>
       </c>
-      <c r="G2" t="n">
-        <v>5</v>
-      </c>
-      <c r="W2" t="n">
+      <c r="H2">
+        <v>5</v>
+      </c>
+      <c r="X2">
         <v>1</v>
       </c>
-      <c r="X2" t="n">
+      <c r="Y2">
         <v>0</v>
       </c>
-      <c r="Y2" t="n">
+      <c r="Z2">
         <v>0</v>
       </c>
-      <c r="Z2" t="n">
+      <c r="AA2">
         <v>0</v>
       </c>
-      <c r="AB2" t="n">
+      <c r="AC2">
         <v>0</v>
       </c>
-      <c r="AI2" t="n">
-        <v>12.1575</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="G3" t="n">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="G4" t="n">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="G5" t="n">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="G6" t="n">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="G7" t="n">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="G8" t="n">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="G9" t="n">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="G10" t="n">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="G11" t="n">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="G12" t="n">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="G13" t="n">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="G14" t="n">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="G15" t="n">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="G16" t="n">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="G17" t="n">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="G18" t="n">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="G19" t="n">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="G20" t="n">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="G21" t="n">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="G22" t="n">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="G23" t="n">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="G24" t="n">
+      <c r="AJ2">
+        <v>12.157500000000001</v>
+      </c>
+    </row>
+    <row r="3" spans="1:36" x14ac:dyDescent="0.3">
+      <c r="H3">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="4" spans="1:36" x14ac:dyDescent="0.3">
+      <c r="H4">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="5" spans="1:36" x14ac:dyDescent="0.3">
+      <c r="H5">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="6" spans="1:36" x14ac:dyDescent="0.3">
+      <c r="H6">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="7" spans="1:36" x14ac:dyDescent="0.3">
+      <c r="H7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="8" spans="1:36" x14ac:dyDescent="0.3">
+      <c r="H8">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="9" spans="1:36" x14ac:dyDescent="0.3">
+      <c r="H9">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="10" spans="1:36" x14ac:dyDescent="0.3">
+      <c r="H10">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="11" spans="1:36" x14ac:dyDescent="0.3">
+      <c r="H11">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="12" spans="1:36" x14ac:dyDescent="0.3">
+      <c r="H12">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="13" spans="1:36" x14ac:dyDescent="0.3">
+      <c r="H13">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="14" spans="1:36" x14ac:dyDescent="0.3">
+      <c r="H14">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="15" spans="1:36" x14ac:dyDescent="0.3">
+      <c r="H15">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="16" spans="1:36" x14ac:dyDescent="0.3">
+      <c r="H16">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="17" spans="8:8" x14ac:dyDescent="0.3">
+      <c r="H17">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="18" spans="8:8" x14ac:dyDescent="0.3">
+      <c r="H18">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="19" spans="8:8" x14ac:dyDescent="0.3">
+      <c r="H19">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="20" spans="8:8" x14ac:dyDescent="0.3">
+      <c r="H20">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="21" spans="8:8" x14ac:dyDescent="0.3">
+      <c r="H21">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="22" spans="8:8" x14ac:dyDescent="0.3">
+      <c r="H22">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="23" spans="8:8" x14ac:dyDescent="0.3">
+      <c r="H23">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="24" spans="8:8" x14ac:dyDescent="0.3">
+      <c r="H24">
         <v>5</v>
       </c>
     </row>

--- a/allotted_holdings.xlsx
+++ b/allotted_holdings.xlsx
@@ -8,19 +8,20 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\CapitalFund1\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B5BB23AA-8CD6-44A9-87D6-96040B8AF06E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{00040921-B672-4939-A848-27F62AA86372}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-38520" yWindow="2340" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="1" sheetId="1" r:id="rId1"/>
+    <sheet name="2" sheetId="3" r:id="rId2"/>
   </sheets>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="12">
   <si>
     <t>security_name</t>
   </si>
@@ -649,4 +650,211 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8CFACDDA-46F8-4347-A644-C0B466288384}">
+  <dimension ref="A1:AJ24"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="13.88671875" customWidth="1"/>
+    <col min="3" max="3" width="13.88671875" customWidth="1"/>
+    <col min="4" max="4" width="16.5546875" customWidth="1"/>
+    <col min="5" max="5" width="15.33203125" customWidth="1"/>
+    <col min="7" max="7" width="13.44140625" customWidth="1"/>
+    <col min="8" max="8" width="23.5546875" customWidth="1"/>
+    <col min="9" max="9" width="26.33203125" customWidth="1"/>
+    <col min="10" max="10" width="21.88671875" customWidth="1"/>
+    <col min="11" max="11" width="22.109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:36" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A1" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H1" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="I1" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="J1" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="K1" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="M1" s="1"/>
+      <c r="N1" s="1"/>
+      <c r="O1" s="1"/>
+    </row>
+    <row r="2" spans="1:36" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>10</v>
+      </c>
+      <c r="B2">
+        <v>200</v>
+      </c>
+      <c r="C2">
+        <v>400</v>
+      </c>
+      <c r="D2">
+        <v>500</v>
+      </c>
+      <c r="E2">
+        <v>2</v>
+      </c>
+      <c r="H2">
+        <v>5</v>
+      </c>
+      <c r="X2">
+        <v>1</v>
+      </c>
+      <c r="Y2">
+        <v>0</v>
+      </c>
+      <c r="Z2">
+        <v>0</v>
+      </c>
+      <c r="AA2">
+        <v>0</v>
+      </c>
+      <c r="AC2">
+        <v>0</v>
+      </c>
+      <c r="AJ2">
+        <v>12.157500000000001</v>
+      </c>
+    </row>
+    <row r="3" spans="1:36" x14ac:dyDescent="0.3">
+      <c r="H3">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="4" spans="1:36" x14ac:dyDescent="0.3">
+      <c r="H4">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="5" spans="1:36" x14ac:dyDescent="0.3">
+      <c r="H5">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="6" spans="1:36" x14ac:dyDescent="0.3">
+      <c r="H6">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="7" spans="1:36" x14ac:dyDescent="0.3">
+      <c r="H7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="8" spans="1:36" x14ac:dyDescent="0.3">
+      <c r="H8">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="9" spans="1:36" x14ac:dyDescent="0.3">
+      <c r="H9">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="10" spans="1:36" x14ac:dyDescent="0.3">
+      <c r="H10">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="11" spans="1:36" x14ac:dyDescent="0.3">
+      <c r="H11">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="12" spans="1:36" x14ac:dyDescent="0.3">
+      <c r="H12">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="13" spans="1:36" x14ac:dyDescent="0.3">
+      <c r="H13">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="14" spans="1:36" x14ac:dyDescent="0.3">
+      <c r="H14">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="15" spans="1:36" x14ac:dyDescent="0.3">
+      <c r="H15">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="16" spans="1:36" x14ac:dyDescent="0.3">
+      <c r="H16">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="17" spans="8:8" x14ac:dyDescent="0.3">
+      <c r="H17">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="18" spans="8:8" x14ac:dyDescent="0.3">
+      <c r="H18">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="19" spans="8:8" x14ac:dyDescent="0.3">
+      <c r="H19">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="20" spans="8:8" x14ac:dyDescent="0.3">
+      <c r="H20">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="21" spans="8:8" x14ac:dyDescent="0.3">
+      <c r="H21">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="22" spans="8:8" x14ac:dyDescent="0.3">
+      <c r="H22">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="23" spans="8:8" x14ac:dyDescent="0.3">
+      <c r="H23">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="24" spans="8:8" x14ac:dyDescent="0.3">
+      <c r="H24">
+        <v>5</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>